--- a/data/trans_camb/IP17-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-2.97472701396361</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-7.237860660414055</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-3.203100178137835</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-11.04821960496018</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-3.107089877438118</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-9.054689955709328</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-8.988099682285082</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-14.27669798770342</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.49849131117321</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-18.73532397952174</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-7.414759890896619</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-14.30101285228992</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>3.50274215081234</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.018843190675631</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.960992611041529</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-2.05382662492516</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.317863696108464</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-3.271911304770004</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.1182259517438934</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.2876576442646325</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.119421000137009</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.4119101375482738</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1196225984801784</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3486045089327781</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.3097275217908178</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.5245176880718916</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.3290445037281788</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.6299411398359387</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2578522488220227</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5190904532398077</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.1630753886943407</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.05573893426032537</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.1365281658364802</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0.07681685373533516</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.06443821724479783</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.1306019276729507</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-4.594212016499144</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-4.996746786603176</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.5985292900984623</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-7.998527788016468</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-2.593998954164917</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-6.352121191901563</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-10.78670839128563</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-11.91336048718279</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.647528613038982</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-13.94153196309767</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-7.463601042705531</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-10.71920635898218</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>2.188557738454396</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.348004799316415</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.385160621789175</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-1.564038597592487</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.726388271657698</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-1.642844480222631</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.2025135280943927</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.220257318799235</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.02905055750767913</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.3882210867981361</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1198468194618533</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.293477960144636</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.4090217077376549</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.4603043521542668</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.2868967171873905</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.5829125803258552</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3053681898691253</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4492041758032984</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.1202727520168471</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.1249492459003841</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.3680784939052608</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.08835043149090913</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.09347352792545251</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.08000209505009949</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-0.5553952763764247</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.46250647796019</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.65222546856548</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-3.929628399877233</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-1.114486500327372</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-2.577950407023275</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-7.627494597478771</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-8.510659764883984</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-8.9587883207055</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-10.97847405094709</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-6.544663761053579</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-7.583490958208674</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>7.403898200339578</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>5.43645475214532</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>5.448957583931517</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.976705292423057</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>4.406809090660422</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.558047948766649</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.02780100379524676</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.07320758723339786</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.08232144124441056</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.1957920874526456</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.05566029158870115</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.1287494028092555</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.3331554219523053</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.3568501325001108</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.3816443969816707</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.4624902981771899</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.290433354035995</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.3273653351893582</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.4568541192566714</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.3412839640320096</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.3529801180993505</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.1991885618992322</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.266824418598179</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.1529223850030076</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-4.475479450492364</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-5.781860601318026</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-10.22695217823905</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-8.447241160762193</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-7.040678557665325</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-6.990613016496311</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-13.18861466863375</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-14.07089884865458</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-20.09596278848357</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-17.76831677122771</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-14.01212695578828</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-13.08358725688726</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>4.974869794423718</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.238992507968334</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-0.5900618264547232</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-0.3623972637476602</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.1699342058889472</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-0.6727715407220944</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.2109874970807606</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.2725742147263677</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.4294108208772062</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.3546840444515697</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.3144464679810687</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.3122104714845353</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.5179660478044361</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.5363482260755345</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.6774537728765719</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.5833385102952834</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.5267494765806955</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.5016397394979234</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.3244935987341085</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.1666484549101048</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>-0.0139354420403451</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.01322073505798413</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.004202808923798383</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.03669434902436949</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-2.974668320511959</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-5.236087801259329</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-2.739767905736148</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-8.203519722828045</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-2.861239160375076</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-6.631791072929596</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-6.728029483982889</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-9.076187095606389</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-6.007425338526517</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-11.65555189196709</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-5.310206657475083</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-8.956010744553346</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.5887142507496202</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-1.734585780491691</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.089323263517092</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-4.58331253701227</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.2265239354489941</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-4.129370949599269</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.1307294614608377</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.2301133654801842</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.119037400723141</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.356426419384634</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.1250425766708725</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.2898241626167667</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.2719331262537904</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.3660178614551121</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.2446337744573988</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.473866867644563</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.2173860990528174</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.3747804433993766</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.02840808798331446</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.0827306299934213</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.05252925800853464</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0.2140854858924104</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.007653737596665284</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.186276919503944</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
